--- a/fh6-livery-organizer-demo.xlsx
+++ b/fh6-livery-organizer-demo.xlsx
@@ -1644,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.0" customWidth="1"/>
@@ -1657,19 +1657,21 @@
     <col min="8" max="8" width="24.0" customWidth="1"/>
     <col min="9" max="9" width="20.0" customWidth="1"/>
     <col min="10" max="10" width="12.0" customWidth="1"/>
-    <col min="11" max="11" width="26.0" customWidth="1"/>
-    <col min="12" max="12" width="40.0" customWidth="1"/>
-    <col min="13" max="13" width="20.0" customWidth="1"/>
-    <col min="14" max="14" width="22.0" customWidth="1"/>
-    <col min="15" max="15" width="36.0" customWidth="1"/>
-    <col min="16" max="16" width="12.0" customWidth="1"/>
-    <col min="17" max="17" width="12.0" customWidth="1"/>
-    <col min="18" max="18" width="20.0" customWidth="1"/>
-    <col min="19" max="19" width="30.0" customWidth="1"/>
-    <col min="20" max="20" width="24.0" customWidth="1"/>
-    <col min="21" max="21" width="32.0" customWidth="1"/>
-    <col min="22" max="22" width="48.0" customWidth="1"/>
-    <col min="23" max="23" width="40.0" customWidth="1"/>
+    <col min="11" max="11" width="28.0" customWidth="1"/>
+    <col min="12" max="12" width="12.0" customWidth="1"/>
+    <col min="13" max="13" width="26.0" customWidth="1"/>
+    <col min="14" max="14" width="40.0" customWidth="1"/>
+    <col min="15" max="15" width="20.0" customWidth="1"/>
+    <col min="16" max="16" width="22.0" customWidth="1"/>
+    <col min="17" max="17" width="36.0" customWidth="1"/>
+    <col min="18" max="18" width="12.0" customWidth="1"/>
+    <col min="19" max="19" width="12.0" customWidth="1"/>
+    <col min="20" max="20" width="20.0" customWidth="1"/>
+    <col min="21" max="21" width="30.0" customWidth="1"/>
+    <col min="22" max="22" width="24.0" customWidth="1"/>
+    <col min="23" max="23" width="32.0" customWidth="1"/>
+    <col min="24" max="24" width="48.0" customWidth="1"/>
+    <col min="25" max="25" width="40.0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1725,65 +1727,75 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">作成方法監査</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">監査スコア</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">タイトル</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">取得日時</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">タグ</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">メモ</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">お気に入り</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">後で確認</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Livery参照ID</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ペイントID</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">フィンガープリント</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">サムネイル元</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">保存元</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">解析メモ</t>
         </is>
@@ -1828,7 +1840,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Atelier 10</t>
+          <t xml:space="preserve">Preview Design 09</t>
         </is>
       </c>
       <c r="J2" s="3">
@@ -1836,29 +1848,29 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 001 - レーシング</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レーシング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-10 09:00:00 JST</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1871,30 +1883,40 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">7d8dbdd09b54131c4723341cc33bc2fa</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_0296_001</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">c237ce2f26d163a4662e9de2</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68ca98695e83d073653b18cb</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_001.png</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_0296_001</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1912,11 +1934,11 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002 Acura RSX Type S</t>
+          <t xml:space="preserve">2001 Acura Integra Type R</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1926,50 +1948,50 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RSX Type S</t>
+          <t xml:space="preserve">Integra Type R</t>
         </is>
       </c>
       <c r="G3" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACU_RSXTypeS_02</t>
+          <t xml:space="preserve">ACU_IntegraR_01</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 17</t>
+          <t xml:space="preserve">Demo Creator 31</t>
         </is>
       </c>
       <c r="J3" s="3">
-        <v>5498</v>
+        <v>10546</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 002 - ストリート</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストリート。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-11 01:00:00 JST</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1982,30 +2004,40 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">972721253d3313f4b8f65e538cefd8bc</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_0422_002</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">c3dd8815c0b0c65cf2ffa26b</t>
-        </is>
-      </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_0368_002</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2648cf07b5d4d7944cf66e18</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_002.png</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_0422_002</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_0368_002</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2023,64 +2055,64 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <v>1276</v>
+        <v>1155</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977 Pontiac Firebird Trans Am</t>
+          <t xml:space="preserve">1965 Shelby Cobra Daytona Coupe</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pontiac</t>
+          <t xml:space="preserve">Shelby</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Firebird Trans Am</t>
+          <t xml:space="preserve">Cobra Daytona Coupe</t>
         </is>
       </c>
       <c r="G4" s="3">
-        <v>1977</v>
+        <v>1965</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PON_FirebirdTransAm_77</t>
+          <t xml:space="preserve">SHE_CobraDaytona_65</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 25</t>
+          <t xml:space="preserve">Demo Creator 13</t>
         </is>
       </c>
       <c r="J4" s="3">
-        <v>5647</v>
+        <v>10719</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 003 - クラシック</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: クラシック。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-11 17:00:00 JST</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2093,30 +2125,40 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">35d32bd78433638498c380ff292933df</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_1276_003</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0bebdbc6dcb6c85930ec0192</t>
-        </is>
-      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_1155_003</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8153c5ed2d8888310108bd29</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_003.png</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1276_003</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1155_003</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2134,34 +2176,34 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <v>1382</v>
+        <v>1276</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990 Subaru LEGACY RS</t>
+          <t xml:space="preserve">1977 Pontiac Firebird Trans Am</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subaru</t>
+          <t xml:space="preserve">Pontiac</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEGACY RS</t>
+          <t xml:space="preserve">Firebird Trans Am</t>
         </is>
       </c>
       <c r="G5" s="3">
-        <v>1990</v>
+        <v>1977</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUB_LegacyRS_90</t>
+          <t xml:space="preserve">PON_FirebirdTransAm_77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 37</t>
+          <t xml:space="preserve">Demo Creator 26</t>
         </is>
       </c>
       <c r="J5" s="3">
@@ -2169,29 +2211,29 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 004 - スポーツ</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: スポーツ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-12 09:00:00 JST</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2204,30 +2246,40 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">e0d5685ea313cd3b86518a93e0d32313</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_1382_004</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47de311962cd6fc96d595b4c</t>
-        </is>
-      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_1276_004</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">409fe0b1aa644e74abcb3960</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_004.png</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1382_004</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1276_004</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2245,34 +2297,34 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <v>1393</v>
+        <v>1376</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992 Alfa Romeo 155 Q4</t>
+          <t xml:space="preserve">1999 Lotus Elise Series 1 Sport 190</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alfa Romeo</t>
+          <t xml:space="preserve">Lotus</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155 Q4</t>
+          <t xml:space="preserve">Elise Series 1 Sport 190</t>
         </is>
       </c>
       <c r="G6" s="3">
-        <v>1992</v>
+        <v>1999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALF_155_92</t>
+          <t xml:space="preserve">LOT_Elise_99</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 38</t>
+          <t xml:space="preserve">Demo Creator 18</t>
         </is>
       </c>
       <c r="J6" s="3">
@@ -2280,29 +2332,29 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 005 - ツーリング</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ツーリング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-13 01:00:00 JST</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2315,30 +2367,40 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">f283b4f591cbd1c7578b0d7bcc15ae80</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_1393_005</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">549f983cb0ab325a373af8f0</t>
-        </is>
-      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_1376_005</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76aad4146f144043bfab1794</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_005.png</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1393_005</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1376_005</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2356,64 +2418,64 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <v>1514</v>
+        <v>1382</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973 Mazda RX-3</t>
+          <t xml:space="preserve">1990 Subaru LEGACY RS</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mazda</t>
+          <t xml:space="preserve">Subaru</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RX-3</t>
+          <t xml:space="preserve">LEGACY RS</t>
         </is>
       </c>
       <c r="G7" s="3">
-        <v>1973</v>
+        <v>1990</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAZ_RX3_73</t>
+          <t xml:space="preserve">SUB_LegacyRS_90</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 26</t>
+          <t xml:space="preserve">Demo Creator 38</t>
         </is>
       </c>
       <c r="J7" s="3">
-        <v>1878</v>
+        <v>6094</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 006 - レトロ</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レトロ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-12 06:00:00 JST</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2426,30 +2488,40 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">46d5cc7694efc74e9df97f938a3e8d62</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_1514_006</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">f83118584245b620324d9fc4</t>
-        </is>
-      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_1382_006</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28eeae571d17f1ec1f73bff4</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_006.png</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1514_006</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1382_006</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2467,34 +2539,34 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <v>2002</v>
+        <v>1393</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012 Nissan GT-R Black Edition (R35)</t>
+          <t xml:space="preserve">1992 Alfa Romeo 155 Q4</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissan</t>
+          <t xml:space="preserve">Alfa Romeo</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT-R Black Edition (R35)</t>
+          <t xml:space="preserve">155 Q4</t>
         </is>
       </c>
       <c r="G8" s="3">
-        <v>2012</v>
+        <v>1992</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIS_GTR_12</t>
+          <t xml:space="preserve">ALF_155_92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemoWorks 01</t>
+          <t xml:space="preserve">Demo Creator 39</t>
         </is>
       </c>
       <c r="J8" s="3">
@@ -2502,29 +2574,29 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 007 - シンプル</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: シンプル。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-12 22:00:00 JST</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2537,30 +2609,40 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035644d86c14f3f6384a52731c14410</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2002_007</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9bce94dae2a7710302820239</t>
-        </is>
-      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_1393_007</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09aeb2077ae46cf5c50269c8</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_007.png</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2002_007</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1393_007</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2578,64 +2660,64 @@
         </is>
       </c>
       <c r="C9" s="3">
-        <v>2017</v>
+        <v>1514</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968 Abarth 595 esseesse</t>
+          <t xml:space="preserve">1973 Mazda RX-3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abarth</t>
+          <t xml:space="preserve">Mazda</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595 esseesse</t>
+          <t xml:space="preserve">RX-3</t>
         </is>
       </c>
       <c r="G9" s="3">
-        <v>1968</v>
+        <v>1973</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIA_595SS_68</t>
+          <t xml:space="preserve">MAZ_RX3_73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 23</t>
+          <t xml:space="preserve">Demo Creator 27</t>
         </is>
       </c>
       <c r="J9" s="3">
-        <v>6392</v>
+        <v>2104</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 008 - ストライプ</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストライプ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-13 14:00:00 JST</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2648,30 +2730,40 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">42be7b196179b007d8f2eb6173207718</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2017_008</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96a10f4a536c5f082d1e780a</t>
-        </is>
-      </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_1514_008</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2e34167ae0b6abfb48810532</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_008.png</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2017_008</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_1514_008</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2689,34 +2781,34 @@
         </is>
       </c>
       <c r="C10" s="3">
-        <v>2131</v>
+        <v>2002</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014 HSV GEN-F GTS</t>
+          <t xml:space="preserve">2012 Nissan GT-R Black Edition (R35)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSV</t>
+          <t xml:space="preserve">Nissan</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEN-F GTS</t>
+          <t xml:space="preserve">GT-R Black Edition (R35)</t>
         </is>
       </c>
       <c r="G10" s="3">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOL_HSVGTS_14</t>
+          <t xml:space="preserve">NIS_GTR_12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sample Works 11</t>
+          <t xml:space="preserve">DemoWorks 01</t>
         </is>
       </c>
       <c r="J10" s="3">
@@ -2724,29 +2816,29 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 009 - テストカラー</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: テストカラー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-14 06:00:00 JST</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2759,30 +2851,40 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">4fe08dc5bd4f3592d7fefd01cee7b91a</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2131_009</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86695cc9fff399ec75b0de72</t>
-        </is>
-      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2002_009</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7f08e8b73b02a5d5a8dba3b5</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_009.png</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2131_009</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2002_009</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2800,64 +2902,64 @@
         </is>
       </c>
       <c r="C11" s="3">
-        <v>2412</v>
+        <v>2017</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957 BMW Isetta 300 Export</t>
+          <t xml:space="preserve">1968 Abarth 595 esseesse</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BMW</t>
+          <t xml:space="preserve">Abarth</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isetta 300 Export</t>
+          <t xml:space="preserve">595 esseesse</t>
         </is>
       </c>
       <c r="G11" s="3">
-        <v>1957</v>
+        <v>1968</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmw_isetta_62</t>
+          <t xml:space="preserve">FIA_595SS_68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 14</t>
+          <t xml:space="preserve">Demo Creator 24</t>
         </is>
       </c>
       <c r="J11" s="3">
-        <v>790</v>
+        <v>6690</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 010 - ショーカー</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ショーカー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-14 22:00:00 JST</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2870,30 +2972,40 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">e4eda8cb922f096131b8ad32cdf6b7e5</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2412_010</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">c01d9cb67a14dffbbd97bca2</t>
-        </is>
-      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2017_010</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5a963b1343e719be1b45764e</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_010.png</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2412_010</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2017_010</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2911,64 +3023,64 @@
         </is>
       </c>
       <c r="C12" s="3">
-        <v>2430</v>
+        <v>2131</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016 Ariel Nomad</t>
+          <t xml:space="preserve">2014 HSV GEN-F GTS</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ariel</t>
+          <t xml:space="preserve">HSV</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomad</t>
+          <t xml:space="preserve">GEN-F GTS</t>
         </is>
       </c>
       <c r="G12" s="3">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI_Nomad_16</t>
+          <t xml:space="preserve">HOL_HSVGTS_14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 18</t>
+          <t xml:space="preserve">Demo Atelier 10</t>
         </is>
       </c>
       <c r="J12" s="3">
-        <v>2443</v>
+        <v>6839</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 011 - レーシング</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レーシング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-14 03:00:00 JST</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -2981,30 +3093,40 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">0765c9bd9bce6cf8c274d4db41537a97</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2430_011</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6433b8c8dcf28e7a3326efe3</t>
-        </is>
-      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2131_011</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226b2d5baf8ab3634cffdb23</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_011.png</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2430_011</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2131_011</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3022,64 +3144,64 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <v>2569</v>
+        <v>2412</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015 Ultima Evolution Coupe 1020</t>
+          <t xml:space="preserve">1957 BMW Isetta 300 Export</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultima</t>
+          <t xml:space="preserve">BMW</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evolution Coupe 1020</t>
+          <t xml:space="preserve">Isetta 300 Export</t>
         </is>
       </c>
       <c r="G13" s="3">
-        <v>2015</v>
+        <v>1957</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ULT_EvolutionCoupe_15</t>
+          <t xml:space="preserve">bmw_isetta_62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 27</t>
+          <t xml:space="preserve">Demo Creator 14</t>
         </is>
       </c>
       <c r="J13" s="3">
-        <v>6988</v>
+        <v>82</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 012 - ストリート</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストリート。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-14 19:00:00 JST</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3092,30 +3214,40 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">0d9542ff93296f55cccf63e0750dc048</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2569_012</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4eb5949ebe53dd6c528e3129</t>
-        </is>
-      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2412_012</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69c41a988b5df4896c1d8d31</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_012.png</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2569_012</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2412_012</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3133,64 +3265,64 @@
         </is>
       </c>
       <c r="C14" s="3">
-        <v>2613</v>
+        <v>2430</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970 GMC Jimmy</t>
+          <t xml:space="preserve">2016 Ariel Nomad</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GMC</t>
+          <t xml:space="preserve">Ariel</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jimmy</t>
+          <t xml:space="preserve">Nomad</t>
         </is>
       </c>
       <c r="G14" s="3">
-        <v>1970</v>
+        <v>2016</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GMC_Jimmy_70</t>
+          <t xml:space="preserve">ARI_Nomad_16</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 32</t>
+          <t xml:space="preserve">Demo Creator 19</t>
         </is>
       </c>
       <c r="J14" s="3">
-        <v>7137</v>
+        <v>2669</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 013 - クラシック</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: クラシック。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-15 11:00:00 JST</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3203,30 +3335,40 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">7e5525e0b6d0061eb0c5942078233983</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2613_013</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">c3c0cc0e62016ac8ccb549a8</t>
-        </is>
-      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2430_013</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b82fdd7390f354d5aa67a10b</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_013.png</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2613_013</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2430_013</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3244,29 +3386,29 @@
         </is>
       </c>
       <c r="C15" s="3">
-        <v>2649</v>
+        <v>2569</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010 Ford Crown Victoria Police Interceptor</t>
+          <t xml:space="preserve">2015 Ultima Evolution Coupe 1020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ford</t>
+          <t xml:space="preserve">Ultima</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crown Victoria Police Interceptor</t>
+          <t xml:space="preserve">Evolution Coupe 1020</t>
         </is>
       </c>
       <c r="G15" s="3">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">for_crownvictoria_10</t>
+          <t xml:space="preserve">ULT_EvolutionCoupe_15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -3275,33 +3417,33 @@
         </is>
       </c>
       <c r="J15" s="3">
-        <v>2782</v>
+        <v>7286</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 014 - スポーツ</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: スポーツ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-16 03:00:00 JST</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3314,30 +3456,40 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">6e55a701cc7f9a6194bb7e395979cb4b</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2649_014</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9352e1f22a91e3a6a6007d69</t>
-        </is>
-      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2569_014</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c881be346cf4301171364f07</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_014.png</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2649_014</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2569_014</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3355,64 +3507,64 @@
         </is>
       </c>
       <c r="C16" s="3">
-        <v>2987</v>
+        <v>2613</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962 Peel P50</t>
+          <t xml:space="preserve">1970 GMC Jimmy</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peel</t>
+          <t xml:space="preserve">GMC</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">P50</t>
+          <t xml:space="preserve">Jimmy</t>
         </is>
       </c>
       <c r="G16" s="3">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEE_P50_62</t>
+          <t xml:space="preserve">GMC_Jimmy_70</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 30</t>
+          <t xml:space="preserve">Demo Creator 33</t>
         </is>
       </c>
       <c r="J16" s="3">
-        <v>2895</v>
+        <v>7435</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 015 - ツーリング</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ツーリング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-16 19:00:00 JST</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3425,30 +3577,40 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">b5fcf9c393f887a2bcd5f6879729c5a2</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_2987_015</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6622047c0f500a4bcc4bf413</t>
-        </is>
-      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2613_015</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ed841db4695c83f10cdf20a3</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_015.png</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2987_015</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2613_015</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3466,64 +3628,64 @@
         </is>
       </c>
       <c r="C17" s="3">
-        <v>3129</v>
+        <v>2649</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008 Renault Mégane R26.R</t>
+          <t xml:space="preserve">2010 Ford Crown Victoria Police Interceptor</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renault</t>
+          <t xml:space="preserve">Ford</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mégane R26.R</t>
+          <t xml:space="preserve">Crown Victoria Police Interceptor</t>
         </is>
       </c>
       <c r="G17" s="3">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REN_MeganeR26R_08</t>
+          <t xml:space="preserve">for_crownvictoria_10</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemoWorks 01</t>
+          <t xml:space="preserve">Demo Creator 29</t>
         </is>
       </c>
       <c r="J17" s="3">
-        <v>7584</v>
+        <v>3008</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 016 - レトロ</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レトロ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-16 00:00:00 JST</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3536,30 +3698,40 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">6f07c514315db7914fe54d222989ef76</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3129_016</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9d050ba4e5b775e80d0806e8</t>
-        </is>
-      </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2649_016</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f55eab9e44161f2659e84dc0</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_016.png</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3129_016</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2649_016</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3577,64 +3749,64 @@
         </is>
       </c>
       <c r="C18" s="3">
-        <v>3149</v>
+        <v>2987</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018 Chevrolet Camaro ZL1 1LE</t>
+          <t xml:space="preserve">1962 Peel P50</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chevrolet</t>
+          <t xml:space="preserve">Peel</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camaro ZL1 1LE</t>
+          <t xml:space="preserve">P50</t>
         </is>
       </c>
       <c r="G18" s="3">
-        <v>2018</v>
+        <v>1962</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHE_Camaro1LE_18</t>
+          <t xml:space="preserve">PEE_P50_62</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 24</t>
+          <t xml:space="preserve">Demo Creator 32</t>
         </is>
       </c>
       <c r="J18" s="3">
-        <v>7733</v>
+        <v>3121</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 017 - シンプル</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: シンプル。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-16 16:00:00 JST</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3647,30 +3819,40 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">45cac3ab8a85d9685b7fd9c0f2e102f6</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3149_017</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71427d88f6dad9a34a8648ac</t>
-        </is>
-      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_2987_017</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a4d18060982ab112deae77b3</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_017.png</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3149_017</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_2987_017</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3688,34 +3870,34 @@
         </is>
       </c>
       <c r="C19" s="3">
-        <v>3211</v>
+        <v>3129</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017 Aston Martin Vulcan AMR Pro</t>
+          <t xml:space="preserve">2008 Renault Mégane R26.R</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aston Martin</t>
+          <t xml:space="preserve">Renault</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vulcan AMR Pro</t>
+          <t xml:space="preserve">Mégane R26.R</t>
         </is>
       </c>
       <c r="G19" s="3">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AST_VulcanAMRPro_19</t>
+          <t xml:space="preserve">REN_MeganeR26R_08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 16</t>
+          <t xml:space="preserve">DemoWorks 01</t>
         </is>
       </c>
       <c r="J19" s="3">
@@ -3723,29 +3905,29 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 018 - ストライプ</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストライプ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-17 08:00:00 JST</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3758,30 +3940,40 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2a19388404acf448104a2dccfcef30f9</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3211_018</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76c7ce8e447dfefde52a9dc1</t>
-        </is>
-      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3129_018</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3c75d0a604a7b357f4ea9507</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_018.png</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3211_018</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3129_018</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3799,34 +3991,34 @@
         </is>
       </c>
       <c r="C20" s="3">
-        <v>3359</v>
+        <v>3149</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021 Audi RS e-tron GT</t>
+          <t xml:space="preserve">2018 Chevrolet Camaro ZL1 1LE</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audi</t>
+          <t xml:space="preserve">Chevrolet</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RS e-tron GT</t>
+          <t xml:space="preserve">Camaro ZL1 1LE</t>
         </is>
       </c>
       <c r="G20" s="3">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUD_Etron_18</t>
+          <t xml:space="preserve">CHE_Camaro1LE_18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 22</t>
+          <t xml:space="preserve">Demo Creator 25</t>
         </is>
       </c>
       <c r="J20" s="3">
@@ -3834,29 +4026,29 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 019 - テストカラー</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: テストカラー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18 00:00:00 JST</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3869,30 +4061,40 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2a778f8a3e39261950503a5d81ddd315</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3359_019</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da47fcd27700ff69c3dd220e</t>
-        </is>
-      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3149_019</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b450e0f156ba1f9da8144177</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_019.png</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3359_019</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3149_019</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3910,64 +4112,64 @@
         </is>
       </c>
       <c r="C21" s="3">
-        <v>3367</v>
+        <v>3211</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019 Ferrari F8 Tributo</t>
+          <t xml:space="preserve">2017 Aston Martin Vulcan AMR Pro</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrari</t>
+          <t xml:space="preserve">Aston Martin</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8 Tributo</t>
+          <t xml:space="preserve">Vulcan AMR Pro</t>
         </is>
       </c>
       <c r="G21" s="3">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FER_F8Tributo_20</t>
+          <t xml:space="preserve">AST_VulcanAMRPro_19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 15</t>
+          <t xml:space="preserve">Demo Creator 16</t>
         </is>
       </c>
       <c r="J21" s="3">
-        <v>13660</v>
+        <v>8180</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 020 - ショーカー</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ショーカー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18 16:00:00 JST</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3980,30 +4182,40 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">76ba5b31fc0cce95d96bea1c87159c95</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3367_020</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bfc59d1bb32f5f9dd9c3f32a</t>
-        </is>
-      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3211_020</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">467a426c79d8a4c19da612c2</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_020.png</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3367_020</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3211_020</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4021,34 +4233,34 @@
         </is>
       </c>
       <c r="C22" s="3">
-        <v>3523</v>
+        <v>3359</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020 Formula Drift #151 Toyota GR Supra</t>
+          <t xml:space="preserve">2021 Audi RS e-tron GT</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formula Drift</t>
+          <t xml:space="preserve">Audi</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#151 Toyota GR Supra</t>
+          <t xml:space="preserve">RS e-tron GT</t>
         </is>
       </c>
       <c r="G22" s="3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOY_151_SupraGRFD_20</t>
+          <t xml:space="preserve">AUD_Etron_18</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 36</t>
+          <t xml:space="preserve">Demo Creator 23</t>
         </is>
       </c>
       <c r="J22" s="3">
@@ -4056,29 +4268,29 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 021 - レーシング</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レーシング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-17 21:00:00 JST</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4091,30 +4303,40 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">6c7c5215ee37821cd9da0b05e01dfcca</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3523_021</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">725cf804d14a3b06c470418d</t>
-        </is>
-      </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3359_021</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c0dc8d30912ac46e6a8f6588</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_021.png</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3523_021</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3359_021</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4132,64 +4354,64 @@
         </is>
       </c>
       <c r="C23" s="3">
-        <v>3761</v>
+        <v>3367</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022 Toyota GR86</t>
+          <t xml:space="preserve">2019 Ferrari F8 Tributo</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toyota</t>
+          <t xml:space="preserve">Ferrari</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GR86</t>
+          <t xml:space="preserve">F8 Tributo</t>
         </is>
       </c>
       <c r="G23" s="3">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOY_GR86_22</t>
+          <t xml:space="preserve">FER_F8Tributo_20</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo ReDownload 90</t>
+          <t xml:space="preserve">Demo Creator 15</t>
         </is>
       </c>
       <c r="J23" s="3">
-        <v>8478</v>
+        <v>14006</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">デモ再DL完全一致</t>
+          <t xml:space="preserve">3/5</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">再ダウンロード完全一致の整理機能を確認するためのダミーデータです。</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">デモペイント 022 - ストリート</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストリート。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18 13:00:00 JST</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4202,30 +4424,40 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">064a5b862207c414cb9418a232a781ac</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3761_022</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">f732dfeca14885528985c557</t>
-        </is>
-      </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3367_022</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b9df89559e72c1edbdfa382b</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_022.png</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_022</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3367_022</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4243,34 +4475,34 @@
         </is>
       </c>
       <c r="C24" s="3">
-        <v>3761</v>
+        <v>3523</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022 Toyota GR86</t>
+          <t xml:space="preserve">2020 Formula Drift #151 Toyota GR Supra</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toyota</t>
+          <t xml:space="preserve">Formula Drift</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GR86</t>
+          <t xml:space="preserve">#151 Toyota GR Supra</t>
         </is>
       </c>
       <c r="G24" s="3">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOY_GR86_22</t>
+          <t xml:space="preserve">TOY_151_SupraGRFD_20</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo ReDownload 90</t>
+          <t xml:space="preserve">Demo Creator 37</t>
         </is>
       </c>
       <c r="J24" s="3">
@@ -4278,29 +4510,29 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">デモ再DL完全一致</t>
+          <t xml:space="preserve">4/5</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">再ダウンロード完全一致の整理機能を確認するためのダミーデータです。</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">デモペイント 023 - クラシック</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: クラシック。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-19 05:00:00 JST</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4313,30 +4545,40 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2c2968b46a78882b3d9dc2a03286b360</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3761_023</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">f732dfeca14885528985c557</t>
-        </is>
-      </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3523_023</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5f7ba8a547bec0b2eb0c93f4</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_023.png</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_023</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3523_023</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4381,37 +4623,37 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preview Similarity 91</t>
+          <t xml:space="preserve">Demo ReDownload 90</t>
         </is>
       </c>
       <c r="J25" s="3">
-        <v>3912</v>
+        <v>8776</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">デモ同一作者・同名</t>
+          <t xml:space="preserve">5/5</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一作者・同名候補の比較用ダミーデータ 2 です。画像内容は異なります。</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">デモ再DL完全一致</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再ダウンロード完全一致の整理機能を確認するためのダミーデータです。</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-19 21:00:00 JST</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4424,30 +4666,40 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">b57a11e7cbef793af39d4f432a6eb388</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_024</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6f53d4d2d06805b66a5e557b</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f732dfeca14885528985c557</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_024.png</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_024</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4492,7 +4744,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sample Racing 02</t>
+          <t xml:space="preserve">Preview Similarity 91</t>
         </is>
       </c>
       <c r="J26" s="3">
@@ -4500,29 +4752,29 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">デモペイント 025 - ツーリング</t>
+          <t xml:space="preserve">0/5</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ツーリング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">デモ同一作者・同名</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一作者・同名候補の比較用ダミーデータ 2 です。画像内容は異なります。</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-20 13:00:00 JST</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4535,30 +4787,40 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">9377546e4a42e106f52c11d6c84499d6</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_025</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75d6568e8a3fc3908695c8f9</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e69800671903c61b2fb1e03c</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_025.png</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_025</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4603,37 +4865,37 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preview Similarity 91</t>
+          <t xml:space="preserve">Demo ReDownload 90</t>
         </is>
       </c>
       <c r="J27" s="3">
-        <v>9074</v>
+        <v>4138</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">デモ同一作者・同名</t>
+          <t xml:space="preserve">1/5</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一作者・同名候補の比較用ダミーデータ 1 です。画像内容は異なります。</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">デモ再DL完全一致</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再ダウンロード完全一致の整理機能を確認するためのダミーデータです。</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-19 18:00:00 JST</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4646,30 +4908,40 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ce332a358f95faee75bfc4dc04819c8c</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_026</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3fc23530096bd7fdc1ecd971</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f732dfeca14885528985c557</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_026.png</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_026</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4714,7 +4986,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sample Racing 02</t>
+          <t xml:space="preserve">Preview Similarity 91</t>
         </is>
       </c>
       <c r="J28" s="3">
@@ -4722,29 +4994,29 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">デモペイント 027 - シンプル</t>
+          <t xml:space="preserve">2/5</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: シンプル。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">デモ同一作者・同名</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一作者・同名候補の比較用ダミーデータ 1 です。画像内容は異なります。</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-20 10:00:00 JST</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4757,30 +5029,40 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">4a2f1140e870289b2db116c71564cfbe</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_027</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ec94fd77b92b3d8919d91aad</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_027.png</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_027</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4833,29 +5115,29 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 028 - ストライプ</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストライプ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-21 02:00:00 JST</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4868,30 +5150,40 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">30e12f277462c6a1f888dca65265d386</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_028</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">78ebc68d044197c8aeadd80c</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_028.png</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_028</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4944,29 +5236,29 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 029 - テストカラー</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: テストカラー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-21 18:00:00 JST</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -4979,30 +5271,40 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">b283df2c61f98c2e172da213effe6c3a</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_029</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0073d597c63eb900e6fd1d44</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_029.png</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_029</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5055,29 +5357,29 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 030 - ショーカー</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ショーカー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-22 10:00:00 JST</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5090,30 +5392,40 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">3d1bc7dfe5268cedf0c555c866ae12f0</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_030</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">4d8e96a50def4d4105ad93fc</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="W31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_030.png</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_030</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5166,29 +5478,29 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 031 - レーシング</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レーシング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-21 15:00:00 JST</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5201,30 +5513,40 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">7a05d1ca9ee8c2a412e159f1595dc48a</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_031</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">24e5c2d1045b024ea11a1ba6</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_031.png</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_031</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5269,7 +5591,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preview Studio 03</t>
+          <t xml:space="preserve">Demo Creator 17</t>
         </is>
       </c>
       <c r="J33" s="3">
@@ -5277,29 +5599,29 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 032 - ストリート</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストリート。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-22 07:00:00 JST</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5312,30 +5634,40 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">9bf0f063989f1a7c9ffd78872e1d81c3</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_032</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60e3722f517ce18672bf2620</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14c958ce05658ec48501761d</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_032.png</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_032</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5384,33 +5716,33 @@
         </is>
       </c>
       <c r="J34" s="3">
-        <v>11409</v>
+        <v>5617</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 033 - クラシック</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: クラシック。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-22 23:00:00 JST</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5423,30 +5755,40 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">630ae04855e1e09bdb41027c4f2de58d</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_033</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">530f9843a38c9253a613b2e9</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_033.png</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_033</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5491,7 +5833,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 35</t>
+          <t xml:space="preserve">Preview Studio 03</t>
         </is>
       </c>
       <c r="J35" s="3">
@@ -5499,29 +5841,29 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 034 - スポーツ</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: スポーツ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-23 15:00:00 JST</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5534,30 +5876,40 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ac4343a7e09b4b602753249e4373242a</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_034</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">021282de50b2ab6304337edd</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44c44ab5388a265400f672ae</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_034.png</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_034</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5602,37 +5954,37 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 33</t>
+          <t xml:space="preserve">Preview Studio 03</t>
         </is>
       </c>
       <c r="J36" s="3">
-        <v>5915</v>
+        <v>11755</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 035 - ツーリング</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ツーリング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-24 07:00:00 JST</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5645,30 +5997,40 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">d35bf1101b7b9455386e735ee9e14ef6</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_035</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07d44c129036499edb5cc93f</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b517d925be89bf582c0e30c3</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_035.png</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_035</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5713,37 +6075,37 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemoWorks 01</t>
+          <t xml:space="preserve">Demo Creator 36</t>
         </is>
       </c>
       <c r="J37" s="3">
-        <v>1768</v>
+        <v>11928</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 036 - レトロ</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レトロ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-23 12:00:00 JST</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5756,30 +6118,40 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">738489e8eaa274890077c4187d6dd20a</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_036</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">f89e91758b034effed852770</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980ab731202485f66a088bc0</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_036.png</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_036</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5824,7 +6196,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Graphics 04</t>
+          <t xml:space="preserve">Demo Creator 34</t>
         </is>
       </c>
       <c r="J38" s="3">
@@ -5832,29 +6204,29 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 037 - シンプル</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: シンプル。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-24 04:00:00 JST</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5867,30 +6239,40 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">6e831236cabb067538bc89603f413ab9</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_037</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59cecb7a3778eafca3a61a2c</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53faccdc008ba58ed9ac459a</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_037.png</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_037</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5935,37 +6317,37 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preview Factory 12</t>
+          <t xml:space="preserve">DemoWorks 01</t>
         </is>
       </c>
       <c r="J39" s="3">
-        <v>12274</v>
+        <v>1994</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 038 - ストライプ</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストライプ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-24 20:00:00 JST</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -5978,30 +6360,40 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">a6f5b663a8dba02ddfd40d3b601463b2</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_038</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3e3aa09598f98ae0e092fbfd</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198eda3a35c2506fac0b7528</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_038.png</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_038</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6046,7 +6438,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 20</t>
+          <t xml:space="preserve">Demo Graphics 04</t>
         </is>
       </c>
       <c r="J40" s="3">
@@ -6054,29 +6446,29 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 039 - テストカラー</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: テストカラー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-25 12:00:00 JST</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6089,30 +6481,40 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">4559865d7c1d15ad1119c71d7a8d855c</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_3761_039</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4bb1141c17154bca288d96e8</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7d26988ab55db23174aa7d3f</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_039.png</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_039</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6130,64 +6532,64 @@
         </is>
       </c>
       <c r="C41" s="3">
-        <v>3854</v>
+        <v>3761</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993 Autozam AZ-1</t>
+          <t xml:space="preserve">2022 Toyota GR86</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autozam</t>
+          <t xml:space="preserve">Toyota</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ-1</t>
+          <t xml:space="preserve">GR86</t>
         </is>
       </c>
       <c r="G41" s="3">
-        <v>1993</v>
+        <v>2022</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZM_AZ1_93</t>
+          <t xml:space="preserve">TOY_GR86_22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sample Livery 05</t>
+          <t xml:space="preserve">Sample Works 11</t>
         </is>
       </c>
       <c r="J41" s="3">
-        <v>6660</v>
+        <v>12620</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 040 - ショーカー</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ショーカー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-26 04:00:00 JST</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6200,30 +6602,40 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">81f4870c2e2a26aa26c3dcb62cfea469</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3854_040</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">309610db78e49d8f58076cf7</t>
-        </is>
-      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3761_040</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e82e8ea5d895b509b76f324c</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_040.png</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3854_040</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_040</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6241,34 +6653,34 @@
         </is>
       </c>
       <c r="C42" s="3">
-        <v>3865</v>
+        <v>3761</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994 Honda Acty</t>
+          <t xml:space="preserve">2022 Toyota GR86</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Honda</t>
+          <t xml:space="preserve">Toyota</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acty</t>
+          <t xml:space="preserve">GR86</t>
         </is>
       </c>
       <c r="G42" s="3">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HON_Acty_94</t>
+          <t xml:space="preserve">TOY_GR86_22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 29</t>
+          <t xml:space="preserve">Demo Creator 21</t>
         </is>
       </c>
       <c r="J42" s="3">
@@ -6276,29 +6688,29 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 041 - レーシング</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レーシング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-25 09:00:00 JST</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6311,30 +6723,40 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">b2db655bf27a0f05189e942a79a45892</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3865_041</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b1d752d2713b71ce0b0e360e</t>
-        </is>
-      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3761_041</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5fe7bb5e1204f456c14d3fe6</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_041.png</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3865_041</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3761_041</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6352,64 +6774,64 @@
         </is>
       </c>
       <c r="C43" s="3">
-        <v>3891</v>
+        <v>3854</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024 Lamborghini Revuelto</t>
+          <t xml:space="preserve">1993 Autozam AZ-1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamborghini</t>
+          <t xml:space="preserve">Autozam</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revuelto</t>
+          <t xml:space="preserve">AZ-1</t>
         </is>
       </c>
       <c r="G43" s="3">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAM_Revuelto_24</t>
+          <t xml:space="preserve">AZM_AZ1_93</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemoWorks 01</t>
+          <t xml:space="preserve">Sample Livery 05</t>
         </is>
       </c>
       <c r="J43" s="3">
-        <v>2446</v>
+        <v>6958</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 042 - ストリート</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストリート。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-26 01:00:00 JST</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6422,30 +6844,40 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">7e1a20a363caee1906215987391c9004</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3891_042</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7db0de3d385085925d37a99c</t>
-        </is>
-      </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3854_042</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54d7434d76777b532e849879</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_042.png</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3891_042</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3854_042</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6463,64 +6895,64 @@
         </is>
       </c>
       <c r="C44" s="3">
-        <v>3928</v>
+        <v>3865</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021 Hyundai i20 N</t>
+          <t xml:space="preserve">1994 Honda Acty</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyundai</t>
+          <t xml:space="preserve">Honda</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">i20 N</t>
+          <t xml:space="preserve">Acty</t>
         </is>
       </c>
       <c r="G44" s="3">
-        <v>2021</v>
+        <v>1994</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HYU_i20N_22</t>
+          <t xml:space="preserve">HON_Acty_94</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 31</t>
+          <t xml:space="preserve">Demo Creator 30</t>
         </is>
       </c>
       <c r="J44" s="3">
-        <v>2559</v>
+        <v>7107</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 043 - クラシック</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: クラシック。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-26 17:00:00 JST</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6533,30 +6965,40 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">caed87ef25fdca757eec8d4853a2143d</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3928_043</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fc079e567b7d5c5cc23741af</t>
-        </is>
-      </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3865_043</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a4273812cc0b4487406c986d</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_043.png</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3928_043</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3865_043</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6574,29 +7016,29 @@
         </is>
       </c>
       <c r="C45" s="3">
-        <v>3933</v>
+        <v>3891</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997 Toyota Chaser 2.5 Tourer V</t>
+          <t xml:space="preserve">2024 Lamborghini Revuelto</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toyota</t>
+          <t xml:space="preserve">Lamborghini</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaser 2.5 Tourer V</t>
+          <t xml:space="preserve">Revuelto</t>
         </is>
       </c>
       <c r="G45" s="3">
-        <v>1997</v>
+        <v>2024</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOY_Chaser_97</t>
+          <t xml:space="preserve">LAM_Revuelto_24</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -6605,33 +7047,33 @@
         </is>
       </c>
       <c r="J45" s="3">
-        <v>7256</v>
+        <v>2672</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 044 - スポーツ</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: スポーツ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-27 09:00:00 JST</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6644,30 +7086,40 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">9e19f15198dc420e77c949b1ca8fa966</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3933_044</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a324b8c97f13f3bc61434dea</t>
-        </is>
-      </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3891_044</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06073336ae40762ea41922cd</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_044.png</t>
         </is>
       </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3933_044</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3891_044</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6685,64 +7137,64 @@
         </is>
       </c>
       <c r="C46" s="3">
-        <v>3953</v>
+        <v>3933</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023 Porsche 911 Turbo S</t>
+          <t xml:space="preserve">1997 Toyota Chaser 2.5 Tourer V</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Porsche</t>
+          <t xml:space="preserve">Toyota</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911 Turbo S</t>
+          <t xml:space="preserve">Chaser 2.5 Tourer V</t>
         </is>
       </c>
       <c r="G46" s="3">
-        <v>2023</v>
+        <v>1997</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POR_911TurboS_23</t>
+          <t xml:space="preserve">TOY_Chaser_97</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 21</t>
+          <t xml:space="preserve">DemoWorks 01</t>
         </is>
       </c>
       <c r="J46" s="3">
-        <v>13485</v>
+        <v>7405</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 045 - ツーリング</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ツーリング。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-28 01:00:00 JST</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6755,30 +7207,40 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">dce06160e032b8ca374469e0f191c35d</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_3953_045</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182b3c47a189d060581d97c0</t>
-        </is>
-      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3933_045</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2df469d119ce38ba872b54f2</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_045.png</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3953_045</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3933_045</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6796,64 +7258,64 @@
         </is>
       </c>
       <c r="C47" s="3">
-        <v>4002</v>
+        <v>3953</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024 Lamborghini Temerario</t>
+          <t xml:space="preserve">2023 Porsche 911 Turbo S</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamborghini</t>
+          <t xml:space="preserve">Porsche</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temerario</t>
+          <t xml:space="preserve">911 Turbo S</t>
         </is>
       </c>
       <c r="G47" s="3">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAM_Temerario_24</t>
+          <t xml:space="preserve">POR_911TurboS_23</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemoWorks 01</t>
+          <t xml:space="preserve">Demo Creator 22</t>
         </is>
       </c>
       <c r="J47" s="3">
-        <v>7554</v>
+        <v>13658</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 046 - レトロ</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: レトロ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-27 06:00:00 JST</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6866,30 +7328,40 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">877c1f0ff8260a99b2c9aca4236aefc1</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_4002_046</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42d32c2e3b186f65971a7b70</t>
-        </is>
-      </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_3953_046</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07b97be78cfdee3924d357c6</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_046.png</t>
         </is>
       </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4002_046</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_3953_046</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6907,34 +7379,34 @@
         </is>
       </c>
       <c r="C48" s="3">
-        <v>4163</v>
+        <v>4002</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013 Wuling Sunshine S Forza Edition</t>
+          <t xml:space="preserve">2024 Lamborghini Temerario</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wuling</t>
+          <t xml:space="preserve">Lamborghini</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunshine S Forza Edition</t>
+          <t xml:space="preserve">Temerario</t>
         </is>
       </c>
       <c r="G48" s="3">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">WUL_HongguangSFE_20</t>
+          <t xml:space="preserve">LAM_Temerario_24</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 19</t>
+          <t xml:space="preserve">DemoWorks 01</t>
         </is>
       </c>
       <c r="J48" s="3">
@@ -6942,29 +7414,29 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 047 - シンプル</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: シンプル。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-27 22:00:00 JST</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6977,30 +7449,40 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">e8d26046ff4a012d7b813a0b00d840c3</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_4163_047</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85fcf88e620537d5b0e43f40</t>
-        </is>
-      </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_4002_047</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">577ca9b0dcf0e047f9be6c42</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_047.png</t>
         </is>
       </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4163_047</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4002_047</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7018,34 +7500,34 @@
         </is>
       </c>
       <c r="C49" s="3">
-        <v>4198</v>
+        <v>4118</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999 Dodge Viper GTS ACR Forza Edition</t>
+          <t xml:space="preserve">2025 McLaren W1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dodge</t>
+          <t xml:space="preserve">McLaren</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viper GTS ACR Forza Edition</t>
+          <t xml:space="preserve">W1</t>
         </is>
       </c>
       <c r="G49" s="3">
-        <v>1999</v>
+        <v>2025</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOD_ViperGTSACRFE_99</t>
+          <t xml:space="preserve">MCL_W1_25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preview Garage 06</t>
+          <t xml:space="preserve">Demo Paint Lab 07</t>
         </is>
       </c>
       <c r="J49" s="3">
@@ -7053,29 +7535,29 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 048 - ストライプ</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ストライプ。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-28 14:00:00 JST</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -7088,30 +7570,40 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">42810c3b8604882718adbe1e503a9ff9</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_4198_048</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14317b6f4aa061ddb1e74a43</t>
-        </is>
-      </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_4118_048</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ab26ddb0c6919d6fed79a027</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_048.png</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4198_048</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4118_048</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7129,34 +7621,34 @@
         </is>
       </c>
       <c r="C50" s="3">
-        <v>4221</v>
+        <v>4163</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025 GR GT Prototype</t>
+          <t xml:space="preserve">2013 Wuling Sunshine S Forza Edition</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GR</t>
+          <t xml:space="preserve">Wuling</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Prototype</t>
+          <t xml:space="preserve">Sunshine S Forza Edition</t>
         </is>
       </c>
       <c r="G50" s="3">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOY_Scallop_26</t>
+          <t xml:space="preserve">WUL_HongguangSFE_20</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sample Motorsport 08</t>
+          <t xml:space="preserve">Demo Creator 20</t>
         </is>
       </c>
       <c r="J50" s="3">
@@ -7164,29 +7656,29 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">0/5</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 049 - テストカラー</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: テストカラー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-29 06:00:00 JST</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -7199,30 +7691,40 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">e96a0fa60642f97bdd0e8f49e98dd9f5</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DemoLivery_4221_049</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">d37f7101a9cea2e676235f6c</t>
-        </is>
-      </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">DemoLivery_4163_049</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62b95ace8e567263ef6df09e</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_049.png</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4221_049</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4163_049</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7267,7 +7769,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demo Creator 13</t>
+          <t xml:space="preserve">Preview Factory 12</t>
         </is>
       </c>
       <c r="J51" s="3">
@@ -7275,29 +7777,29 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">デモペイント 050 - ショーカー</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">プレビュー版の機能確認用ダミーデータです。テーマ: ショーカー。作成者・タイトル・説明・画像・識別情報・FH6表示日付は実データから置き換えています。</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-29 22:00:00 JST</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -7310,37 +7812,47 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">05ae30f45b13f183672b122fb4b6b1b6</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DemoLivery_4267_050</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ffc37ffef3b524ad57068694</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48e9a4432e62f39686d6aa4d</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">_demo-source-thumbnails/demo_050.png</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C:\Demo\FH6\GameSave\pgs\DemoProfile\ContainersRoot\DemoLivery_4267_050</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W51"/>
+  <autoFilter ref="A1:Y51"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <drawing r:id="rId1"/>
 </worksheet>
